--- a/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13665" windowHeight="9975" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="10080" windowHeight="10710"/>
   </bookViews>
   <sheets>
     <sheet name="炼狱" sheetId="8" r:id="rId1"/>
@@ -176,10 +176,10 @@
     <t>传记·钢铁守卫</t>
   </si>
   <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
     <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>白袍主教</t>
   </si>
   <si>
     <t>召集护卫</t>
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1356,7 +1356,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>23</v>
+        <v>23.4285714285714</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1422,7 +1422,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>19.25</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>22.2</v>
+        <v>22.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1561,7 +1561,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1572,7 +1572,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C11" s="1">
         <f>AVERAGE(C2:C8)</f>
-        <v>22</v>
+        <v>22.2857142857143</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1639,7 +1639,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1650,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C14:C17)</f>
-        <v>22.75</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1683,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1705,7 +1705,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1716,7 +1716,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1727,7 +1727,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C30" s="3">
         <f>AVERAGE(C23:C27)</f>
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C33" s="4">
         <f>AVERAGE(C2:C8,C14:C17,C23:C27)</f>
-        <v>22</v>
+        <v>22.6875</v>
       </c>
     </row>
   </sheetData>
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1878,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C17" s="2">
         <f>AVERAGE(C10:C14)</f>
-        <v>22</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C20:C26)</f>
-        <v>19.7142857142857</v>
+        <v>19.8571428571429</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -2033,14 +2033,14 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C4,C10:C14,C20:C26)</f>
-        <v>20.9333333333333</v>
+        <v>21.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32 C7" formulaRange="1"/>
+    <ignoredError sqref="C7 C32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/qieCard/z_level.xlsx
@@ -9,11 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="10080" windowHeight="10710"/>
+    <workbookView windowWidth="12480" windowHeight="10200" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="炼狱" sheetId="8" r:id="rId1"/>
-    <sheet name="港口" sheetId="6" r:id="rId2"/>
+    <sheet name="港口" sheetId="6" r:id="rId1"/>
+    <sheet name="炼狱" sheetId="8" r:id="rId2"/>
     <sheet name="帝国" sheetId="5" r:id="rId3"/>
     <sheet name="隐秘" sheetId="9" r:id="rId4"/>
     <sheet name="企鹅" sheetId="10" r:id="rId5"/>
@@ -47,6 +47,72 @@
     <t>卡等</t>
   </si>
   <si>
+    <t>心灵黑洞1</t>
+  </si>
+  <si>
+    <t>心灵黑洞2</t>
+  </si>
+  <si>
+    <t>黑金勒索者1</t>
+  </si>
+  <si>
+    <t>黑金勒索者2</t>
+  </si>
+  <si>
+    <t>酗酒醉汉</t>
+  </si>
+  <si>
+    <t>不法交易</t>
+  </si>
+  <si>
+    <t>热血矿工</t>
+  </si>
+  <si>
+    <t>小计：</t>
+  </si>
+  <si>
+    <t>蓝色卡等：</t>
+  </si>
+  <si>
+    <t>海燕精卫</t>
+  </si>
+  <si>
+    <t>红海猎魔人</t>
+  </si>
+  <si>
+    <t>黑水伏击</t>
+  </si>
+  <si>
+    <t>星辰陨落</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花剑绅士·翔</t>
+  </si>
+  <si>
+    <t>海燕·鲍莉</t>
+  </si>
+  <si>
+    <t>赤影·艾希尔</t>
+  </si>
+  <si>
+    <t>魔卡幻术师·梅基</t>
+  </si>
+  <si>
+    <t>钢之咆哮·布瑞恩</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>港口卡等：</t>
+  </si>
+  <si>
     <t>冥河守卫1</t>
   </si>
   <si>
@@ -59,12 +125,6 @@
     <t>烈焰风暴</t>
   </si>
   <si>
-    <t>小计：</t>
-  </si>
-  <si>
-    <t>蓝色卡等：</t>
-  </si>
-  <si>
     <t>碎颅魔</t>
   </si>
   <si>
@@ -86,9 +146,6 @@
     <t>雷光炼狱</t>
   </si>
   <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
     <t>痛苦之心</t>
   </si>
   <si>
@@ -101,66 +158,9 @@
     <t>血翼·莉莉丝</t>
   </si>
   <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
     <t>炼狱卡等：</t>
   </si>
   <si>
-    <t>心灵黑洞1</t>
-  </si>
-  <si>
-    <t>心灵黑洞2</t>
-  </si>
-  <si>
-    <t>黑金勒索者1</t>
-  </si>
-  <si>
-    <t>黑金勒索者2</t>
-  </si>
-  <si>
-    <t>酗酒醉汉</t>
-  </si>
-  <si>
-    <t>不法交易</t>
-  </si>
-  <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>海燕精卫</t>
-  </si>
-  <si>
-    <t>红海猎魔人</t>
-  </si>
-  <si>
-    <t>黑水伏击</t>
-  </si>
-  <si>
-    <t>星辰陨落</t>
-  </si>
-  <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>海燕·鲍莉</t>
-  </si>
-  <si>
-    <t>赤影·艾希尔</t>
-  </si>
-  <si>
-    <t>魔卡幻术师·梅基</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
-  </si>
-  <si>
-    <t>港口卡等：</t>
-  </si>
-  <si>
     <t>增援战线</t>
   </si>
   <si>
@@ -173,7 +173,7 @@
     <t>四芒军旗</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
+    <t>符文·民兵集结</t>
   </si>
   <si>
     <t>白袍主教</t>
@@ -215,22 +215,10 @@
     <t>沉重否定2</t>
   </si>
   <si>
-    <t>符文·静默进军</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
     <t>破魔系教授</t>
   </si>
   <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
+    <t>克隆术</t>
   </si>
   <si>
     <t>学仆-脉冲型1</t>
@@ -239,6 +227,15 @@
     <t>学仆-脉冲型2</t>
   </si>
   <si>
+    <t>学仆-猛禽型1</t>
+  </si>
+  <si>
+    <t>学仆-猛禽型2</t>
+  </si>
+  <si>
+    <t>改造魔卷</t>
+  </si>
+  <si>
     <t>米拉方舟</t>
   </si>
   <si>
@@ -252,6 +249,9 @@
   </si>
   <si>
     <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>No.9迪宁</t>
   </si>
   <si>
     <t>隐秘卡等：</t>
@@ -1218,6 +1218,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>22.2857142857143</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C14:C17)</f>
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C8,C14:C17,C23:C27)</f>
+        <v>22.75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
@@ -1239,7 +1522,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1250,7 +1533,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -1261,18 +1544,18 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -1293,20 +1576,20 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <f>AVERAGE(C2:C5)</f>
-        <v>23.75</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1317,7 +1600,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
@@ -1328,7 +1611,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
@@ -1339,7 +1622,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
@@ -1350,7 +1633,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1361,18 +1644,18 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
         <v>5</v>
@@ -1393,19 +1676,19 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>23.4285714285714</v>
+        <v>23.5714285714286</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -1416,7 +1699,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B24" s="3">
         <v>3</v>
@@ -1427,24 +1710,24 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3">
         <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1459,309 +1742,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>19.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>22.4666666666667</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>22.2857142857143</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C14:C17)</f>
-        <v>23.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" s="3">
-        <v>3</v>
-      </c>
-      <c r="C24" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3">
-        <v>4</v>
-      </c>
-      <c r="C25" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>22.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C8,C14:C17,C23:C27)</f>
-        <v>22.6875</v>
+        <v>22.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <f>AVERAGE(C2:C4)</f>
@@ -1864,10 +1864,10 @@
         <v>45</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1915,7 +1915,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1999,7 +1999,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2014,33 +2014,33 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C20:C26)</f>
-        <v>19.8571428571429</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C4,C10:C14,C20:C26)</f>
-        <v>21.2</v>
+        <v>21.2666666666667</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C7 C32" formulaRange="1"/>
+    <ignoredError sqref="C32 C7" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2090,59 +2090,59 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <f>AVERAGE(C2:C3)</f>
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B9" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="C9" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>12</v>
-      </c>
-      <c r="D8" s="2"/>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2150,10 +2150,10 @@
         <v>62</v>
       </c>
       <c r="B12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2161,10 +2161,10 @@
         <v>63</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2172,10 +2172,10 @@
         <v>64</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2183,10 +2183,10 @@
         <v>65</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2194,10 +2194,10 @@
         <v>66</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2212,15 +2212,9 @@
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="2">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -2228,20 +2222,26 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="A20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C11:C18)</f>
-        <v>14.875</v>
+      <c r="C20" s="2">
+        <f>AVERAGE(C9:C17)</f>
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2249,10 +2249,10 @@
         <v>69</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2260,10 +2260,10 @@
         <v>70</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2271,10 +2271,10 @@
         <v>71</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2289,26 +2289,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C24:C26)</f>
-        <v>19.3333333333333</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C18,C24:C26)</f>
-        <v>15</v>
+        <f>AVERAGE(C2:C3,C9:C17,C23:C26)</f>
+        <v>16.6666666666667</v>
       </c>
     </row>
   </sheetData>
